--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0003_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0003_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -914,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="0">
-        <v>0.0038042582330488559</v>
+        <v>0</v>
       </c>
       <c r="D23" s="0">
         <v>0</v>
@@ -923,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="0">
-        <v>0.0036386129607393625</v>
+        <v>0</v>
       </c>
       <c r="G23" s="0">
         <v>0</v>
@@ -932,16 +933,16 @@
         <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>0.0059581736211793161</v>
+        <v>0</v>
       </c>
       <c r="J23" s="0">
         <v>0</v>
       </c>
       <c r="K23" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L23" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -952,16 +953,16 @@
         <v>0</v>
       </c>
       <c r="C24" s="0">
-        <v>0.0088766025437806897</v>
+        <v>0</v>
       </c>
       <c r="D24" s="0">
         <v>0</v>
       </c>
       <c r="E24" s="0">
-        <v>0.00059667651182911303</v>
+        <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>0.0072772259214787458</v>
+        <v>0</v>
       </c>
       <c r="G24" s="0">
         <v>0</v>
@@ -984,2890 +985,2890 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.027074923697942281</v>
+        <v>0</v>
       </c>
       <c r="B25" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C25" s="0">
-        <v>0.021557463320610183</v>
+        <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>0.002404250715264586</v>
+        <v>0</v>
       </c>
       <c r="E25" s="0">
-        <v>0.0023867060473164452</v>
+        <v>0</v>
       </c>
       <c r="F25" s="0">
-        <v>0.038205436087763313</v>
+        <v>0</v>
       </c>
       <c r="G25" s="0">
-        <v>0.020116676725005011</v>
+        <v>0</v>
       </c>
       <c r="H25" s="0">
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>0.0099302893686321926</v>
+        <v>0</v>
       </c>
       <c r="J25" s="0">
-        <v>0.018402649981597335</v>
+        <v>0</v>
       </c>
       <c r="K25" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L25" s="0">
-        <v>0.015550648462040852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.034458993797381085</v>
+        <v>0</v>
       </c>
       <c r="B26" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0">
-        <v>0.065940476039513501</v>
+        <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>0.002404250715264586</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0">
-        <v>0.0095468241892657808</v>
+        <v>0</v>
       </c>
       <c r="F26" s="0">
-        <v>0.072772259214787263</v>
+        <v>0</v>
       </c>
       <c r="G26" s="0">
-        <v>0.060350030175015036</v>
+        <v>0</v>
       </c>
       <c r="H26" s="0">
-        <v>0.017042549565414972</v>
+        <v>0</v>
       </c>
       <c r="I26" s="0">
-        <v>0.02780481023217014</v>
+        <v>0</v>
       </c>
       <c r="J26" s="0">
-        <v>0.092013249907986677</v>
+        <v>0</v>
       </c>
       <c r="K26" s="0">
         <v>0</v>
       </c>
       <c r="L26" s="0">
-        <v>0.027991167231673539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.10583833809195618</v>
+        <v>0</v>
       </c>
       <c r="B27" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C27" s="0">
-        <v>0.15470650147732015</v>
+        <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>0.024042507152645855</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>0.037590620245234012</v>
+        <v>0</v>
       </c>
       <c r="F27" s="0">
-        <v>0.20558163228177401</v>
+        <v>0</v>
       </c>
       <c r="G27" s="0">
-        <v>0.10058338362502504</v>
+        <v>0</v>
       </c>
       <c r="H27" s="0">
-        <v>0.06248934840652156</v>
+        <v>0</v>
       </c>
       <c r="I27" s="0">
-        <v>0.051637504716887404</v>
+        <v>0</v>
       </c>
       <c r="J27" s="0">
-        <v>0.14722119985277868</v>
+        <v>0</v>
       </c>
       <c r="K27" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L27" s="0">
-        <v>0.073088047771592016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.24121295658166758</v>
+        <v>0</v>
       </c>
       <c r="B28" s="0">
-        <v>0.52631578947368374</v>
+        <v>0</v>
       </c>
       <c r="C28" s="0">
-        <v>0.31702151942073803</v>
+        <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>0.045680763590027124</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0">
-        <v>0.079357976073271802</v>
+        <v>0</v>
       </c>
       <c r="F28" s="0">
-        <v>0.41662118400465709</v>
+        <v>0</v>
       </c>
       <c r="G28" s="0">
-        <v>0.30175015087507517</v>
+        <v>0</v>
       </c>
       <c r="H28" s="0">
-        <v>0.17610634550928805</v>
+        <v>0</v>
       </c>
       <c r="I28" s="0">
-        <v>0.14895434052948289</v>
+        <v>0</v>
       </c>
       <c r="J28" s="0">
-        <v>0.44166359955833606</v>
+        <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L28" s="0">
-        <v>0.20682362454514336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.47011912966427311</v>
+        <v>0</v>
       </c>
       <c r="B29" s="0">
-        <v>1.1403508771929878</v>
+        <v>0</v>
       </c>
       <c r="C29" s="0">
-        <v>0.61755791983160102</v>
+        <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>0.10578703147164235</v>
+        <v>0</v>
       </c>
       <c r="E29" s="0">
-        <v>0.18795310122617112</v>
+        <v>0</v>
       </c>
       <c r="F29" s="0">
-        <v>0.90601462722410631</v>
+        <v>0</v>
       </c>
       <c r="G29" s="0">
-        <v>0.54315027157513829</v>
+        <v>0</v>
       </c>
       <c r="H29" s="0">
-        <v>0.36357439072885472</v>
+        <v>0</v>
       </c>
       <c r="I29" s="0">
-        <v>0.3118110861750526</v>
+        <v>0</v>
       </c>
       <c r="J29" s="0">
-        <v>0.55207949944792301</v>
+        <v>0</v>
       </c>
       <c r="K29" s="0">
-        <v>0.51546391752577558</v>
+        <v>0</v>
       </c>
       <c r="L29" s="0">
-        <v>0.40742698970547264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.84670670473564946</v>
+        <v>0</v>
       </c>
       <c r="B30" s="0">
-        <v>2.6315789473684186</v>
+        <v>0</v>
       </c>
       <c r="C30" s="0">
-        <v>1.1311327812931933</v>
+        <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>0.20916981222801898</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0">
-        <v>0.39977326292550458</v>
+        <v>0</v>
       </c>
       <c r="F30" s="0">
-        <v>1.3772150056398489</v>
+        <v>0</v>
       </c>
       <c r="G30" s="0">
-        <v>0.90525045262522552</v>
+        <v>0</v>
       </c>
       <c r="H30" s="0">
-        <v>0.57944668522410903</v>
+        <v>0</v>
       </c>
       <c r="I30" s="0">
-        <v>0.68916208218307418</v>
+        <v>0</v>
       </c>
       <c r="J30" s="0">
-        <v>1.2145748987854241</v>
+        <v>0</v>
       </c>
       <c r="K30" s="0">
-        <v>2.0618556701030908</v>
+        <v>0</v>
       </c>
       <c r="L30" s="0">
-        <v>0.76820203402481813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>1.4694299497883221</v>
+        <v>0</v>
       </c>
       <c r="B31" s="0">
-        <v>3.4210526315789447</v>
+        <v>0</v>
       </c>
       <c r="C31" s="0">
-        <v>1.8615503620385736</v>
+        <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>0.47844589233765256</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0">
-        <v>0.74524896327456003</v>
+        <v>0</v>
       </c>
       <c r="F31" s="0">
-        <v>2.2213732125313808</v>
+        <v>0</v>
       </c>
       <c r="G31" s="0">
-        <v>1.3679340173003409</v>
+        <v>0</v>
       </c>
       <c r="H31" s="0">
-        <v>1.2497869681304312</v>
+        <v>0</v>
       </c>
       <c r="I31" s="0">
-        <v>1.1896486663621366</v>
+        <v>0</v>
       </c>
       <c r="J31" s="0">
-        <v>2.1531100478468881</v>
+        <v>0</v>
       </c>
       <c r="K31" s="0">
-        <v>3.6082474226804089</v>
+        <v>0</v>
       </c>
       <c r="L31" s="0">
-        <v>1.3451310919665338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>2.1586098257359438</v>
+        <v>0</v>
       </c>
       <c r="B32" s="0">
-        <v>4.4736842105263115</v>
+        <v>0</v>
       </c>
       <c r="C32" s="0">
-        <v>2.669321193522614</v>
+        <v>0</v>
       </c>
       <c r="D32" s="0">
-        <v>0.968913038251628</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0">
-        <v>1.1844028759807861</v>
+        <v>0</v>
       </c>
       <c r="F32" s="0">
-        <v>2.878142851944836</v>
+        <v>0</v>
       </c>
       <c r="G32" s="0">
-        <v>2.6352846509756565</v>
+        <v>0</v>
       </c>
       <c r="H32" s="0">
-        <v>2.1359995455320098</v>
+        <v>0</v>
       </c>
       <c r="I32" s="0">
-        <v>1.8331314174495028</v>
+        <v>0</v>
       </c>
       <c r="J32" s="0">
-        <v>2.8156054471843919</v>
+        <v>0</v>
       </c>
       <c r="K32" s="0">
-        <v>4.2525773195876253</v>
+        <v>0</v>
       </c>
       <c r="L32" s="0">
-        <v>2.1319939041458009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>2.7961012109874939</v>
+        <v>0</v>
       </c>
       <c r="B33" s="0">
-        <v>5.7894736842105212</v>
+        <v>0</v>
       </c>
       <c r="C33" s="0">
-        <v>3.5760027390659244</v>
+        <v>0</v>
       </c>
       <c r="D33" s="0">
-        <v>1.670954247108887</v>
+        <v>0</v>
       </c>
       <c r="E33" s="0">
-        <v>1.7852561233927011</v>
+        <v>0</v>
       </c>
       <c r="F33" s="0">
-        <v>3.5967689116908601</v>
+        <v>0</v>
       </c>
       <c r="G33" s="0">
-        <v>3.3594850130758371</v>
+        <v>0</v>
       </c>
       <c r="H33" s="0">
-        <v>2.7268079304663955</v>
+        <v>0</v>
       </c>
       <c r="I33" s="0">
-        <v>2.6712478401620601</v>
+        <v>0</v>
       </c>
       <c r="J33" s="0">
-        <v>3.8829591461170376</v>
+        <v>0</v>
       </c>
       <c r="K33" s="0">
-        <v>6.3144329896907161</v>
+        <v>0</v>
       </c>
       <c r="L33" s="0">
-        <v>2.8239977607066189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>3.4508220931377345</v>
+        <v>0</v>
       </c>
       <c r="B34" s="0">
-        <v>7.0175438596491162</v>
+        <v>0</v>
       </c>
       <c r="C34" s="0">
-        <v>4.2354074994610595</v>
+        <v>0</v>
       </c>
       <c r="D34" s="0">
-        <v>2.5869737696246942</v>
+        <v>0</v>
       </c>
       <c r="E34" s="0">
-        <v>2.4803842596736159</v>
+        <v>0</v>
       </c>
       <c r="F34" s="0">
-        <v>4.0625113706654989</v>
+        <v>0</v>
       </c>
       <c r="G34" s="0">
-        <v>4.2043854355260475</v>
+        <v>0</v>
       </c>
       <c r="H34" s="0">
-        <v>3.6471056069988039</v>
+        <v>0</v>
       </c>
       <c r="I34" s="0">
-        <v>3.4259498321781066</v>
+        <v>0</v>
       </c>
       <c r="J34" s="0">
-        <v>4.913507545086488</v>
+        <v>0</v>
       </c>
       <c r="K34" s="0">
-        <v>10.695876288659784</v>
+        <v>0</v>
       </c>
       <c r="L34" s="0">
-        <v>3.6217460268093147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>3.8618686620065157</v>
+        <v>0</v>
       </c>
       <c r="B35" s="0">
-        <v>6.666666666666698</v>
+        <v>0</v>
       </c>
       <c r="C35" s="0">
-        <v>4.5498928467264577</v>
+        <v>0</v>
       </c>
       <c r="D35" s="0">
-        <v>3.6232058279037509</v>
+        <v>0</v>
       </c>
       <c r="E35" s="0">
-        <v>3.0525970345177504</v>
+        <v>0</v>
       </c>
       <c r="F35" s="0">
-        <v>4.2589964705454477</v>
+        <v>0</v>
       </c>
       <c r="G35" s="0">
-        <v>4.727419030376204</v>
+        <v>0</v>
       </c>
       <c r="H35" s="0">
-        <v>4.3060841901948734</v>
+        <v>0</v>
       </c>
       <c r="I35" s="0">
-        <v>4.1071676828662973</v>
+        <v>0</v>
       </c>
       <c r="J35" s="0">
-        <v>5.6680161943320106</v>
+        <v>0</v>
       </c>
       <c r="K35" s="0">
-        <v>9.7938144329897359</v>
+        <v>0</v>
       </c>
       <c r="L35" s="0">
-        <v>4.0898205455167673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>3.9332480063010697</v>
+        <v>0</v>
       </c>
       <c r="B36" s="0">
-        <v>5.7017543859649065</v>
+        <v>0</v>
       </c>
       <c r="C36" s="0">
-        <v>4.620905667076677</v>
+        <v>0</v>
       </c>
       <c r="D36" s="0">
-        <v>4.7435866612170274</v>
+        <v>0</v>
       </c>
       <c r="E36" s="0">
-        <v>3.6343566335511173</v>
+        <v>0</v>
       </c>
       <c r="F36" s="0">
-        <v>4.1371029363606553</v>
+        <v>0</v>
       </c>
       <c r="G36" s="0">
-        <v>4.9084691209012226</v>
+        <v>0</v>
       </c>
       <c r="H36" s="0">
-        <v>4.4708288359938608</v>
+        <v>0</v>
       </c>
       <c r="I36" s="0">
-        <v>4.8936466008619446</v>
+        <v>0</v>
       </c>
       <c r="J36" s="0">
-        <v>5.1159366948840592</v>
+        <v>0</v>
       </c>
       <c r="K36" s="0">
-        <v>10.180412371134011</v>
+        <v>0</v>
       </c>
       <c r="L36" s="0">
-        <v>4.2235561222902955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>3.8643300187063074</v>
+        <v>0</v>
       </c>
       <c r="B37" s="0">
-        <v>5.350877192982451</v>
+        <v>0</v>
       </c>
       <c r="C37" s="0">
-        <v>4.4243523250358194</v>
+        <v>0</v>
       </c>
       <c r="D37" s="0">
-        <v>5.8495419902387367</v>
+        <v>0</v>
       </c>
       <c r="E37" s="0">
-        <v>3.8575136489752047</v>
+        <v>0</v>
       </c>
       <c r="F37" s="0">
-        <v>4.2917439871920786</v>
+        <v>0</v>
       </c>
       <c r="G37" s="0">
-        <v>4.8280024140012028</v>
+        <v>0</v>
       </c>
       <c r="H37" s="0">
-        <v>4.4424245867181691</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I37" s="0">
-        <v>4.889674485114492</v>
+        <v>0</v>
       </c>
       <c r="J37" s="0">
-        <v>4.2326094957673872</v>
+        <v>0</v>
       </c>
       <c r="K37" s="0">
-        <v>10.695876288659784</v>
+        <v>0</v>
       </c>
       <c r="L37" s="0">
-        <v>4.3261904021397655</v>
+        <v>0.0031101296924081708</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>3.6428079157231434</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B38" s="0">
-        <v>5.6140350877192935</v>
+        <v>0</v>
       </c>
       <c r="C38" s="0">
-        <v>4.2975437172675246</v>
+        <v>0</v>
       </c>
       <c r="D38" s="0">
-        <v>5.5658404058375162</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E38" s="0">
-        <v>3.844983442226793</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F38" s="0">
-        <v>4.0243059345777352</v>
+        <v>0</v>
       </c>
       <c r="G38" s="0">
-        <v>3.560651780325887</v>
+        <v>0</v>
       </c>
       <c r="H38" s="0">
-        <v>4.1470203942509762</v>
+        <v>0</v>
       </c>
       <c r="I38" s="0">
-        <v>4.7129153343528385</v>
+        <v>0</v>
       </c>
       <c r="J38" s="0">
-        <v>4.1958041958041923</v>
+        <v>0</v>
       </c>
       <c r="K38" s="0">
-        <v>10.051546391752568</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L38" s="0">
-        <v>4.0742698970547035</v>
+        <v>0.0031101296924081708</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>3.5886580683272586</v>
+        <v>0.029536280397755216</v>
       </c>
       <c r="B39" s="0">
-        <v>3.3333333333333304</v>
+        <v>0</v>
       </c>
       <c r="C39" s="0">
-        <v>4.0464626738862997</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D39" s="0">
-        <v>5.6355636765801886</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E39" s="0">
-        <v>3.8008293803514395</v>
+        <v>0.0011933530236582226</v>
       </c>
       <c r="F39" s="0">
-        <v>3.5803951533675331</v>
+        <v>0.0054579194411090446</v>
       </c>
       <c r="G39" s="0">
-        <v>3.6813518406759171</v>
+        <v>0</v>
       </c>
       <c r="H39" s="0">
-        <v>3.5959779583025586</v>
+        <v>0</v>
       </c>
       <c r="I39" s="0">
-        <v>4.5957379198029784</v>
+        <v>0</v>
       </c>
       <c r="J39" s="0">
-        <v>2.9996319470003656</v>
+        <v>0</v>
       </c>
       <c r="K39" s="0">
-        <v>5.9278350515463867</v>
+        <v>0</v>
       </c>
       <c r="L39" s="0">
-        <v>3.8285696513544583</v>
+        <v>0.023325972693061282</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>3.3868268189425978</v>
+        <v>0.03692035049719402</v>
       </c>
       <c r="B40" s="0">
-        <v>2.0175438596491211</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C40" s="0">
-        <v>3.7357815848539762</v>
+        <v>0.0038042582330488559</v>
       </c>
       <c r="D40" s="0">
-        <v>5.1402880292356841</v>
+        <v>0.026446757867910439</v>
       </c>
       <c r="E40" s="0">
-        <v>3.7566753184760846</v>
+        <v>0.0029833825591455568</v>
       </c>
       <c r="F40" s="0">
-        <v>3.5458283302405089</v>
+        <v>0.0072772259214787249</v>
       </c>
       <c r="G40" s="0">
-        <v>2.6956346811506715</v>
+        <v>0</v>
       </c>
       <c r="H40" s="0">
-        <v>2.8631483269897151</v>
+        <v>0.022723399420553292</v>
       </c>
       <c r="I40" s="0">
-        <v>4.452741752894676</v>
+        <v>0</v>
       </c>
       <c r="J40" s="0">
-        <v>2.7972027972027949</v>
+        <v>0</v>
       </c>
       <c r="K40" s="0">
-        <v>3.9948453608247383</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L40" s="0">
-        <v>3.7974683544303764</v>
+        <v>0.035766491462693964</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3.3499064684454227</v>
+        <v>0.091070197893079089</v>
       </c>
       <c r="B41" s="0">
-        <v>1.3157894736842166</v>
+        <v>0.087719298245614447</v>
       </c>
       <c r="C41" s="0">
-        <v>3.6952028303681423</v>
+        <v>0.012680860776829591</v>
       </c>
       <c r="D41" s="0">
-        <v>4.3012045296083681</v>
+        <v>0.067319020027408777</v>
       </c>
       <c r="E41" s="0">
-        <v>3.6755273128673465</v>
+        <v>0.022673707449506357</v>
       </c>
       <c r="F41" s="0">
-        <v>3.151038824000306</v>
+        <v>0.025470290725175683</v>
       </c>
       <c r="G41" s="0">
-        <v>2.5347012673506453</v>
+        <v>0</v>
       </c>
       <c r="H41" s="0">
-        <v>2.6131909333636432</v>
+        <v>0.051127648696245198</v>
       </c>
       <c r="I41" s="0">
-        <v>4.1508609560882803</v>
+        <v>0.005958173621179349</v>
       </c>
       <c r="J41" s="0">
-        <v>2.4107471475892641</v>
+        <v>0.036805299963194871</v>
       </c>
       <c r="K41" s="0">
-        <v>2.7061855670103219</v>
+        <v>0</v>
       </c>
       <c r="L41" s="0">
-        <v>3.5953099244238653</v>
+        <v>0.10885453923428658</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>3.3326769715467135</v>
+        <v>0.30520823077680392</v>
       </c>
       <c r="B42" s="0">
-        <v>0.78947368421052566</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C42" s="0">
-        <v>3.4479260452199467</v>
+        <v>0.038042582330488559</v>
       </c>
       <c r="D42" s="0">
-        <v>3.5799293150289682</v>
+        <v>0.14185079220061056</v>
       </c>
       <c r="E42" s="0">
-        <v>3.5800590709746682</v>
+        <v>0.05668426862376557</v>
       </c>
       <c r="F42" s="0">
-        <v>3.1273878397554826</v>
+        <v>0.072772259214787263</v>
       </c>
       <c r="G42" s="0">
-        <v>2.7962180647756965</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H42" s="0">
-        <v>2.3916377890132341</v>
+        <v>0.12497869681304312</v>
       </c>
       <c r="I42" s="0">
-        <v>3.7476912077217897</v>
+        <v>0.035749041727075895</v>
       </c>
       <c r="J42" s="0">
-        <v>2.2267206477732771</v>
+        <v>0.073610599926389339</v>
       </c>
       <c r="K42" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L42" s="0">
-        <v>3.4740148664199269</v>
+        <v>0.26125089416228631</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>3.1973023530570019</v>
+        <v>0.57349611105641385</v>
       </c>
       <c r="B43" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C43" s="0">
-        <v>3.3426749007722618</v>
+        <v>0.082425595049391884</v>
       </c>
       <c r="D43" s="0">
-        <v>2.9716538840670279</v>
+        <v>0.37025461015074618</v>
       </c>
       <c r="E43" s="0">
-        <v>3.3622721441570427</v>
+        <v>0.12888212655508805</v>
       </c>
       <c r="F43" s="0">
-        <v>3.0054943055707137</v>
+        <v>0.19102718043881656</v>
       </c>
       <c r="G43" s="0">
-        <v>2.7962180647756965</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H43" s="0">
-        <v>2.5109356359711392</v>
+        <v>0.24427654377094793</v>
       </c>
       <c r="I43" s="0">
-        <v>3.5550435939703253</v>
+        <v>0.061567794085519593</v>
       </c>
       <c r="J43" s="0">
-        <v>2.5027603974972377</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K43" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L43" s="0">
-        <v>3.4460236991882529</v>
+        <v>0.48207010232326641</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>2.904400905779263</v>
+        <v>1.0017721768238645</v>
       </c>
       <c r="B44" s="0">
-        <v>0.61403508771929771</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C44" s="0">
-        <v>3.171483280285063</v>
+        <v>0.2016256863515894</v>
       </c>
       <c r="D44" s="0">
-        <v>2.8442285961580049</v>
+        <v>0.78138148246099037</v>
       </c>
       <c r="E44" s="0">
-        <v>3.2041528685223279</v>
+        <v>0.26552104776395452</v>
       </c>
       <c r="F44" s="0">
-        <v>2.8326601899355941</v>
+        <v>0.36204198959356659</v>
       </c>
       <c r="G44" s="0">
-        <v>3.3192516596258268</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H44" s="0">
-        <v>2.7722547293075017</v>
+        <v>0.62489348406521561</v>
       </c>
       <c r="I44" s="0">
-        <v>3.4418382951679183</v>
+        <v>0.1648428035192944</v>
       </c>
       <c r="J44" s="0">
-        <v>2.4291497975708483</v>
+        <v>0.42326094957673871</v>
       </c>
       <c r="K44" s="0">
-        <v>0.64432989690721587</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L44" s="0">
-        <v>3.1085746275619668</v>
+        <v>0.97347059372375733</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>2.9536280397755217</v>
+        <v>1.6712611991729829</v>
       </c>
       <c r="B45" s="0">
-        <v>0.78947368421052566</v>
+        <v>2.9824561403508745</v>
       </c>
       <c r="C45" s="0">
-        <v>2.9318150116029851</v>
+        <v>0.46158333227659448</v>
       </c>
       <c r="D45" s="0">
-        <v>2.8177818382900943</v>
+        <v>1.36321015555502</v>
       </c>
       <c r="E45" s="0">
-        <v>3.1617888361824606</v>
+        <v>0.54595900832363686</v>
       </c>
       <c r="F45" s="0">
-        <v>2.5470290725175539</v>
+        <v>0.75865080231415716</v>
       </c>
       <c r="G45" s="0">
-        <v>2.8565680949507115</v>
+        <v>0.28163347415007012</v>
       </c>
       <c r="H45" s="0">
-        <v>2.7836164290177785</v>
+        <v>1.1248082713173882</v>
       </c>
       <c r="I45" s="0">
-        <v>3.2869257810172559</v>
+        <v>0.34756012790212676</v>
       </c>
       <c r="J45" s="0">
-        <v>3.2020610967979359</v>
+        <v>0.90172984909826925</v>
       </c>
       <c r="K45" s="0">
-        <v>0.25773195876288635</v>
+        <v>1.932989690721648</v>
       </c>
       <c r="L45" s="0">
-        <v>2.9421826890181295</v>
+        <v>1.5846110782819629</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>2.7961012109874939</v>
+        <v>2.3333661514226622</v>
       </c>
       <c r="B46" s="0">
-        <v>0.52631578947368374</v>
+        <v>3.6842105263157858</v>
       </c>
       <c r="C46" s="0">
-        <v>2.77076807973725</v>
+        <v>0.87117513536818803</v>
       </c>
       <c r="D46" s="0">
-        <v>3.221695958454545</v>
+        <v>2.2071021566128897</v>
       </c>
       <c r="E46" s="0">
-        <v>2.9380351442465438</v>
+        <v>0.93439541752438837</v>
       </c>
       <c r="F46" s="0">
-        <v>2.6561874613397349</v>
+        <v>1.3062620529054314</v>
       </c>
       <c r="G46" s="0">
-        <v>3.1382015691007821</v>
+        <v>0.50291691812512529</v>
       </c>
       <c r="H46" s="0">
-        <v>3.1528716696017693</v>
+        <v>1.9485315003124453</v>
       </c>
       <c r="I46" s="0">
-        <v>3.0068916208218281</v>
+        <v>0.72292506603642359</v>
       </c>
       <c r="J46" s="0">
-        <v>2.6683842473316131</v>
+        <v>1.5826278984173707</v>
       </c>
       <c r="K46" s="0">
-        <v>0</v>
+        <v>4.6391752577319547</v>
       </c>
       <c r="L46" s="0">
-        <v>2.8395484091686596</v>
+        <v>2.2532889621497194</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>2.6016540317022865</v>
+        <v>2.9856256768731062</v>
       </c>
       <c r="B47" s="0">
-        <v>0.70175438596491557</v>
+        <v>4.3859649122807216</v>
       </c>
       <c r="C47" s="0">
-        <v>2.5780189959294559</v>
+        <v>1.3669967917422299</v>
       </c>
       <c r="D47" s="0">
-        <v>3.392397759238349</v>
+        <v>3.2625682206140607</v>
       </c>
       <c r="E47" s="0">
-        <v>2.8753841105045033</v>
+        <v>1.4875145439899828</v>
       </c>
       <c r="F47" s="0">
-        <v>2.5161008623512835</v>
+        <v>2.0157915802496182</v>
       </c>
       <c r="G47" s="0">
-        <v>2.7761013880507068</v>
+        <v>0.82478374572521007</v>
       </c>
       <c r="H47" s="0">
-        <v>3.1017440209055418</v>
+        <v>2.4086803385786628</v>
       </c>
       <c r="I47" s="0">
-        <v>2.826160354312738</v>
+        <v>1.2134813608468609</v>
       </c>
       <c r="J47" s="0">
-        <v>2.6499815973500307</v>
+        <v>2.5027603974972514</v>
       </c>
       <c r="K47" s="0">
-        <v>0</v>
+        <v>4.5103092783505368</v>
       </c>
       <c r="L47" s="0">
-        <v>2.6311697197773269</v>
+        <v>3.1552265729481062</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>2.6213448853007755</v>
+        <v>3.5665058580289424</v>
       </c>
       <c r="B48" s="0">
-        <v>0.35087719298245584</v>
+        <v>6.0526315789473628</v>
       </c>
       <c r="C48" s="0">
-        <v>2.4702316793263903</v>
+        <v>2.1037548028760171</v>
       </c>
       <c r="D48" s="0">
-        <v>3.5871420671747618</v>
+        <v>4.4262255668021027</v>
       </c>
       <c r="E48" s="0">
-        <v>2.8103463707151146</v>
+        <v>2.229780124705389</v>
       </c>
       <c r="F48" s="0">
-        <v>2.3869301022450222</v>
+        <v>2.712585962231195</v>
       </c>
       <c r="G48" s="0">
-        <v>2.3536511768255863</v>
+        <v>1.5288674311003809</v>
       </c>
       <c r="H48" s="0">
-        <v>2.8688291768448533</v>
+        <v>3.4369141623586859</v>
       </c>
       <c r="I48" s="0">
-        <v>2.6613175507934277</v>
+        <v>1.9403785426307305</v>
       </c>
       <c r="J48" s="0">
-        <v>2.7972027972027949</v>
+        <v>3.2756716967243253</v>
       </c>
       <c r="K48" s="0">
-        <v>0</v>
+        <v>7.4742268041237043</v>
       </c>
       <c r="L48" s="0">
-        <v>2.5145398563120058</v>
+        <v>3.6901688800422945</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>2.6385743821994661</v>
+        <v>3.8421778084079916</v>
       </c>
       <c r="B49" s="0">
-        <v>1.0526315789473675</v>
+        <v>6.4035087719298192</v>
       </c>
       <c r="C49" s="0">
-        <v>2.3484954158688272</v>
+        <v>2.9368873559137167</v>
       </c>
       <c r="D49" s="0">
-        <v>3.3370999927872451</v>
+        <v>5.3783088500468779</v>
       </c>
       <c r="E49" s="0">
-        <v>2.6122497687878492</v>
+        <v>2.8139264297860889</v>
       </c>
       <c r="F49" s="0">
-        <v>2.2996033911872775</v>
+        <v>3.5894916857693815</v>
       </c>
       <c r="G49" s="0">
-        <v>2.2933011466505713</v>
+        <v>2.4944679139006212</v>
       </c>
       <c r="H49" s="0">
-        <v>2.3916377890132341</v>
+        <v>3.987956598307103</v>
       </c>
       <c r="I49" s="0">
-        <v>2.4527814740521516</v>
+        <v>2.7824670810907408</v>
       </c>
       <c r="J49" s="0">
-        <v>2.0794994479204987</v>
+        <v>4.3614280456385677</v>
       </c>
       <c r="K49" s="0">
-        <v>0</v>
+        <v>10.567010309278341</v>
       </c>
       <c r="L49" s="0">
-        <v>2.3839144092308628</v>
+        <v>4.0556091189002546</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>2.4268977060155539</v>
+        <v>3.925863936201631</v>
       </c>
       <c r="B50" s="0">
-        <v>1.1403508771929816</v>
+        <v>7.2807017543859587</v>
       </c>
       <c r="C50" s="0">
-        <v>2.2204187220228491</v>
+        <v>3.799185888738124</v>
       </c>
       <c r="D50" s="0">
-        <v>3.0269516505181135</v>
+        <v>5.9072440074050867</v>
       </c>
       <c r="E50" s="0">
-        <v>2.6301500641427227</v>
+        <v>3.2787374325009666</v>
       </c>
       <c r="F50" s="0">
-        <v>2.0885638394643942</v>
+        <v>4.0243059345777352</v>
       </c>
       <c r="G50" s="0">
-        <v>1.7702675518004409</v>
+        <v>4.1440354053510324</v>
       </c>
       <c r="H50" s="0">
-        <v>2.1700846446628397</v>
+        <v>4.4878713855592762</v>
       </c>
       <c r="I50" s="0">
-        <v>2.5123632102639446</v>
+        <v>3.612639272308392</v>
       </c>
       <c r="J50" s="0">
-        <v>2.0058888479941093</v>
+        <v>5.2631578947368372</v>
       </c>
       <c r="K50" s="0">
-        <v>0</v>
+        <v>10.309278350515454</v>
       </c>
       <c r="L50" s="0">
-        <v>2.2983858426896382</v>
+        <v>4.3324106615245821</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>2.4367431328148057</v>
+        <v>3.7166486167175314</v>
       </c>
       <c r="B51" s="0">
-        <v>1.7543859649122791</v>
+        <v>5.6140350877192935</v>
       </c>
       <c r="C51" s="0">
-        <v>2.0999505446429687</v>
+        <v>4.2633053931700848</v>
       </c>
       <c r="D51" s="0">
-        <v>2.4475272281393483</v>
+        <v>5.6812444401702162</v>
       </c>
       <c r="E51" s="0">
-        <v>2.4905277603747105</v>
+        <v>3.7393716996330411</v>
       </c>
       <c r="F51" s="0">
-        <v>1.9120911108685354</v>
+        <v>4.3372266492013205</v>
       </c>
       <c r="G51" s="0">
-        <v>1.8507342587004612</v>
+        <v>4.7073023536511727</v>
       </c>
       <c r="H51" s="0">
-        <v>1.9882974492984133</v>
+        <v>4.6923819803442557</v>
       </c>
       <c r="I51" s="0">
-        <v>2.1707612559829972</v>
+        <v>4.1111397986137286</v>
       </c>
       <c r="J51" s="0">
-        <v>1.8402649981597332</v>
+        <v>6.0176665439823278</v>
       </c>
       <c r="K51" s="0">
-        <v>0</v>
+        <v>11.597938144329888</v>
       </c>
       <c r="L51" s="0">
-        <v>2.2113022113022094</v>
+        <v>4.2204459925978872</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>2.3284434380230361</v>
+        <v>3.5271241508319355</v>
       </c>
       <c r="B52" s="0">
-        <v>2.4561403508771908</v>
+        <v>5.7894736842105212</v>
       </c>
       <c r="C52" s="0">
-        <v>2.0657122205455285</v>
+        <v>4.6069567202221649</v>
       </c>
       <c r="D52" s="0">
-        <v>2.2599956723487105</v>
+        <v>5.2749260692905011</v>
       </c>
       <c r="E52" s="0">
-        <v>2.5030579671231221</v>
+        <v>3.871833885259103</v>
       </c>
       <c r="F52" s="0">
-        <v>2.0121529672888676</v>
+        <v>4.2535385511043149</v>
       </c>
       <c r="G52" s="0">
-        <v>1.6898008449004209</v>
+        <v>4.5061355864011219</v>
       </c>
       <c r="H52" s="0">
-        <v>1.7781060046582953</v>
+        <v>4.3117650400499876</v>
       </c>
       <c r="I52" s="0">
-        <v>2.1131655776449305</v>
+        <v>4.7188735079740178</v>
       </c>
       <c r="J52" s="0">
-        <v>1.5090172984909813</v>
+        <v>4.7110783952889177</v>
       </c>
       <c r="K52" s="0">
-        <v>0</v>
+        <v>9.7938144329896826</v>
       </c>
       <c r="L52" s="0">
-        <v>2.0122539109880861</v>
+        <v>3.9405343202811518</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>2.1143054051393109</v>
+        <v>3.4458993797381088</v>
       </c>
       <c r="B53" s="0">
-        <v>2.5438596491228047</v>
+        <v>5.0877192982456094</v>
       </c>
       <c r="C53" s="0">
-        <v>1.9515844735540633</v>
+        <v>4.5955439455230183</v>
       </c>
       <c r="D53" s="0">
-        <v>1.9161878200658746</v>
+        <v>4.6209698747385337</v>
       </c>
       <c r="E53" s="0">
-        <v>2.3091381007786609</v>
+        <v>3.8652704436289835</v>
       </c>
       <c r="F53" s="0">
-        <v>1.8429574646144873</v>
+        <v>4.1480187752428739</v>
       </c>
       <c r="G53" s="0">
-        <v>1.9513176423254861</v>
+        <v>4.6469523234761576</v>
       </c>
       <c r="H53" s="0">
-        <v>1.8633187524853703</v>
+        <v>3.5846162585922823</v>
       </c>
       <c r="I53" s="0">
-        <v>2.0317372048221469</v>
+        <v>4.8062600544179812</v>
       </c>
       <c r="J53" s="0">
-        <v>1.6194331983805654</v>
+        <v>4.1221935958778024</v>
       </c>
       <c r="K53" s="0">
-        <v>0.12886597938144317</v>
+        <v>7.4742268041237043</v>
       </c>
       <c r="L53" s="0">
-        <v>1.9951481976798415</v>
+        <v>3.7663670575062946</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>2.1413803288372533</v>
+        <v>3.3695973220439077</v>
       </c>
       <c r="B54" s="0">
-        <v>4.5614035087719262</v>
+        <v>2.5438596491228047</v>
       </c>
       <c r="C54" s="0">
-        <v>1.798146058154426</v>
+        <v>4.4065991199482584</v>
       </c>
       <c r="D54" s="0">
-        <v>1.9041665664895517</v>
+        <v>3.6953333493616683</v>
       </c>
       <c r="E54" s="0">
-        <v>2.3544855156776734</v>
+        <v>3.8109728810525336</v>
       </c>
       <c r="F54" s="0">
-        <v>1.7629079794782212</v>
+        <v>3.9260633846377728</v>
       </c>
       <c r="G54" s="0">
-        <v>2.3134178233755764</v>
+        <v>4.6067189700261473</v>
       </c>
       <c r="H54" s="0">
-        <v>1.9201272510367535</v>
+        <v>2.9540419246719285</v>
       </c>
       <c r="I54" s="0">
-        <v>1.7675915076165305</v>
+        <v>4.9691168000635493</v>
       </c>
       <c r="J54" s="0">
-        <v>1.987486198012512</v>
+        <v>3.7173352962826613</v>
       </c>
       <c r="K54" s="0">
-        <v>0</v>
+        <v>5.9278350515463867</v>
       </c>
       <c r="L54" s="0">
-        <v>1.8583024912138821</v>
+        <v>3.750816409044254</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.9986216402481027</v>
+        <v>3.5271241508319355</v>
       </c>
       <c r="B55" s="0">
-        <v>3.3333333333333304</v>
+        <v>2.1929824561403488</v>
       </c>
       <c r="C55" s="0">
-        <v>1.7296694099595464</v>
+        <v>4.1605904208777655</v>
       </c>
       <c r="D55" s="0">
-        <v>1.6493159906715056</v>
+        <v>3.301036232058276</v>
       </c>
       <c r="E55" s="0">
-        <v>2.1641457084041869</v>
+        <v>3.6445001342522123</v>
       </c>
       <c r="F55" s="0">
-        <v>1.6355565258523437</v>
+        <v>3.7641451078848704</v>
       </c>
       <c r="G55" s="0">
-        <v>1.890967612150471</v>
+        <v>3.7819352243009421</v>
       </c>
       <c r="H55" s="0">
-        <v>1.8860421519059236</v>
+        <v>2.6870419814804269</v>
       </c>
       <c r="I55" s="0">
-        <v>1.702051597783558</v>
+        <v>4.6016960934241587</v>
       </c>
       <c r="J55" s="0">
-        <v>1.8402649981597332</v>
+        <v>2.8524107471475868</v>
       </c>
       <c r="K55" s="0">
-        <v>0.25773195876288635</v>
+        <v>3.3505154639175228</v>
       </c>
       <c r="L55" s="0">
-        <v>1.6701396448231878</v>
+        <v>3.6932790097347028</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.887860588756521</v>
+        <v>3.0840799448656071</v>
       </c>
       <c r="B56" s="0">
-        <v>2.6315789473684186</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C56" s="0">
-        <v>1.7106481187943021</v>
+        <v>4.0033477472450798</v>
       </c>
       <c r="D56" s="0">
-        <v>1.7070180078378556</v>
+        <v>2.882696607602238</v>
       </c>
       <c r="E56" s="0">
-        <v>2.0859810853545731</v>
+        <v>3.5251648318863893</v>
       </c>
       <c r="F56" s="0">
-        <v>1.6373758323327134</v>
+        <v>3.5058035876723759</v>
       </c>
       <c r="G56" s="0">
-        <v>2.0921343794005214</v>
+        <v>3.0979682156507717</v>
       </c>
       <c r="H56" s="0">
-        <v>2.1814463443731165</v>
+        <v>2.4029994887235109</v>
       </c>
       <c r="I56" s="0">
-        <v>1.5491251415066223</v>
+        <v>4.4428114635260432</v>
       </c>
       <c r="J56" s="0">
-        <v>1.7482517482517468</v>
+        <v>2.5211630474788347</v>
       </c>
       <c r="K56" s="0">
-        <v>0.38659793814432958</v>
+        <v>2.0618556701030908</v>
       </c>
       <c r="L56" s="0">
-        <v>1.657699126053555</v>
+        <v>3.5921997947314375</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.8681697351580384</v>
+        <v>3.2071477798562893</v>
       </c>
       <c r="B57" s="0">
-        <v>2.7192982456140631</v>
+        <v>1.228070175438609</v>
       </c>
       <c r="C57" s="0">
-        <v>1.5559416173169995</v>
+        <v>3.8701987090884127</v>
       </c>
       <c r="D57" s="0">
-        <v>1.8152092900247825</v>
+        <v>2.9067391147549162</v>
       </c>
       <c r="E57" s="0">
-        <v>2.0054297562576653</v>
+        <v>3.427906560458283</v>
       </c>
       <c r="F57" s="0">
-        <v>1.5882545573627496</v>
+        <v>3.1765091147254991</v>
       </c>
       <c r="G57" s="0">
-        <v>2.0116676725005234</v>
+        <v>2.7559847113257172</v>
       </c>
       <c r="H57" s="0">
-        <v>1.9598932000227434</v>
+        <v>2.5961483837982429</v>
       </c>
       <c r="I57" s="0">
-        <v>1.4438640741991369</v>
+        <v>4.0217671942960829</v>
       </c>
       <c r="J57" s="0">
-        <v>1.8402649981597536</v>
+        <v>2.0426941479573268</v>
       </c>
       <c r="K57" s="0">
-        <v>0.38659793814433385</v>
+        <v>1.67525773195878</v>
       </c>
       <c r="L57" s="0">
-        <v>1.5519547165116943</v>
+        <v>3.1707772214101655</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.8509402382593267</v>
+        <v>3.0176233139706579</v>
       </c>
       <c r="B58" s="0">
-        <v>1.0526315789473675</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C58" s="0">
-        <v>1.4380096120924677</v>
+        <v>3.6051687188526329</v>
       </c>
       <c r="D58" s="0">
-        <v>1.7310605149905016</v>
+        <v>3.087057918399728</v>
       </c>
       <c r="E58" s="0">
-        <v>1.8586473343476817</v>
+        <v>3.3407917897311941</v>
       </c>
       <c r="F58" s="0">
-        <v>1.6009897027253197</v>
+        <v>3.0946403231088282</v>
       </c>
       <c r="G58" s="0">
-        <v>1.5087507543753758</v>
+        <v>3.0577348622007618</v>
       </c>
       <c r="H58" s="0">
-        <v>1.7440209055274654</v>
+        <v>2.6756802817701506</v>
       </c>
       <c r="I58" s="0">
-        <v>1.467696768683838</v>
+        <v>3.8509662171555643</v>
       </c>
       <c r="J58" s="0">
-        <v>1.7482517482517468</v>
+        <v>2.6131762973868211</v>
       </c>
       <c r="K58" s="0">
-        <v>0.77319587628865916</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L58" s="0">
-        <v>1.4524305663546158</v>
+        <v>3.0930239790999257</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.6860293393718604</v>
+        <v>2.9585507531751474</v>
       </c>
       <c r="B59" s="0">
-        <v>1.4035087719298234</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C59" s="0">
-        <v>1.4177202348495404</v>
+        <v>3.2780025108104307</v>
       </c>
       <c r="D59" s="0">
-        <v>1.6228692328035952</v>
+        <v>3.3899935085230659</v>
       </c>
       <c r="E59" s="0">
-        <v>1.8216533906142769</v>
+        <v>3.1969927503803786</v>
       </c>
       <c r="F59" s="0">
-        <v>1.4809154750209208</v>
+        <v>3.0418804351781073</v>
       </c>
       <c r="G59" s="0">
-        <v>1.2271172802253056</v>
+        <v>2.4341178837256066</v>
       </c>
       <c r="H59" s="0">
-        <v>1.5963188092938692</v>
+        <v>2.7495313298869486</v>
       </c>
       <c r="I59" s="0">
-        <v>1.2253977080892127</v>
+        <v>3.535183015233061</v>
       </c>
       <c r="J59" s="0">
-        <v>1.3433934486566053</v>
+        <v>2.3739418476260559</v>
       </c>
       <c r="K59" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L59" s="0">
-        <v>1.4353248530463707</v>
+        <v>2.9033060678630274</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.5063503002855161</v>
+        <v>2.7173377965934802</v>
       </c>
       <c r="B60" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C60" s="0">
-        <v>1.2731584219936838</v>
+        <v>3.206989690460186</v>
       </c>
       <c r="D60" s="0">
-        <v>1.4377419277282222</v>
+        <v>3.4669295314115325</v>
       </c>
       <c r="E60" s="0">
-        <v>1.7303618843044226</v>
+        <v>3.0287299740445692</v>
       </c>
       <c r="F60" s="0">
-        <v>1.3335516501109765</v>
+        <v>2.6980315103882378</v>
       </c>
       <c r="G60" s="0">
-        <v>1.1064172198752757</v>
+        <v>2.7559847113256866</v>
       </c>
       <c r="H60" s="0">
-        <v>1.4997443617565174</v>
+        <v>3.1699142191671843</v>
       </c>
       <c r="I60" s="0">
-        <v>1.1797183769935045</v>
+        <v>3.3623959802188606</v>
       </c>
       <c r="J60" s="0">
-        <v>1.10415899889584</v>
+        <v>2.6867868973132105</v>
       </c>
       <c r="K60" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L60" s="0">
-        <v>1.4135539451995136</v>
+        <v>2.764905296550864</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.348823471497488</v>
+        <v>2.5991926750024592</v>
       </c>
       <c r="B61" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C61" s="0">
-        <v>1.1539583306914862</v>
+        <v>3.1334406979545744</v>
       </c>
       <c r="D61" s="0">
-        <v>1.1756785997643824</v>
+        <v>3.3827807563772723</v>
       </c>
       <c r="E61" s="0">
-        <v>1.7029147647602836</v>
+        <v>2.9410185268056894</v>
       </c>
       <c r="F61" s="0">
-        <v>1.2498635520139711</v>
+        <v>2.7216824946330433</v>
       </c>
       <c r="G61" s="0">
-        <v>1.3075839871253259</v>
+        <v>3.0979682156507717</v>
       </c>
       <c r="H61" s="0">
-        <v>1.2554678179855696</v>
+        <v>3.0449355223541414</v>
       </c>
       <c r="I61" s="0">
-        <v>1.2055371293519483</v>
+        <v>3.1776925979623019</v>
       </c>
       <c r="J61" s="0">
-        <v>1.1777695988222294</v>
+        <v>2.5395656974604321</v>
       </c>
       <c r="K61" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L61" s="0">
-        <v>1.2875936926569826</v>
+        <v>2.5627468665443329</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.430048242591315</v>
+        <v>2.6385743821994661</v>
       </c>
       <c r="B62" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C62" s="0">
-        <v>1.1146476622833148</v>
+        <v>2.8975766875055453</v>
       </c>
       <c r="D62" s="0">
-        <v>1.0482533118553594</v>
+        <v>3.0990791719760509</v>
       </c>
       <c r="E62" s="0">
-        <v>1.6002864047256766</v>
+        <v>2.852113726543152</v>
       </c>
       <c r="F62" s="0">
-        <v>1.2589600844158195</v>
+        <v>2.6379943965360382</v>
       </c>
       <c r="G62" s="0">
-        <v>1.2874673104003207</v>
+        <v>3.178434922550792</v>
       </c>
       <c r="H62" s="0">
-        <v>1.334999715957506</v>
+        <v>2.8801908765551301</v>
       </c>
       <c r="I62" s="0">
-        <v>1.0625409624436446</v>
+        <v>3.0247661416853657</v>
       </c>
       <c r="J62" s="0">
-        <v>1.1225616488774373</v>
+        <v>2.7788001472211974</v>
       </c>
       <c r="K62" s="0">
-        <v>0.77319587628865916</v>
+        <v>0</v>
       </c>
       <c r="L62" s="0">
-        <v>1.2269461636550232</v>
+        <v>2.4492271327714343</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.2872895540021649</v>
+        <v>2.6976469429949761</v>
       </c>
       <c r="B63" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C63" s="0">
-        <v>1.0791412521081922</v>
+        <v>2.7454063581835908</v>
       </c>
       <c r="D63" s="0">
-        <v>0.84148775034260492</v>
+        <v>2.687952299665807</v>
       </c>
       <c r="E63" s="0">
-        <v>1.4720009546824175</v>
+        <v>2.7309883946418427</v>
       </c>
       <c r="F63" s="0">
-        <v>1.2371284066513835</v>
+        <v>2.4178583124113065</v>
       </c>
       <c r="G63" s="0">
-        <v>1.4282840474753558</v>
+        <v>3.1583182458257868</v>
       </c>
       <c r="H63" s="0">
-        <v>1.3690848150883359</v>
+        <v>2.5734249843776604</v>
       </c>
       <c r="I63" s="0">
-        <v>1.0307640364640216</v>
+        <v>2.6970665925205037</v>
       </c>
       <c r="J63" s="0">
-        <v>1.1225616488774373</v>
+        <v>3.0364372469635601</v>
       </c>
       <c r="K63" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L63" s="0">
-        <v>1.1196466892669414</v>
+        <v>2.4616676515410672</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.1346854386137628</v>
+        <v>2.3235207246234104</v>
       </c>
       <c r="B64" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C64" s="0">
-        <v>1.0575837887875821</v>
+        <v>2.5716785655410268</v>
       </c>
       <c r="D64" s="0">
-        <v>0.69963695814199434</v>
+        <v>2.3369316952371775</v>
       </c>
       <c r="E64" s="0">
-        <v>1.4165100390823102</v>
+        <v>2.6462603299621086</v>
       </c>
       <c r="F64" s="0">
-        <v>1.0824873558199604</v>
+        <v>2.4433286031364823</v>
       </c>
       <c r="G64" s="0">
-        <v>1.2070006035003007</v>
+        <v>2.6554013277006616</v>
       </c>
       <c r="H64" s="0">
-        <v>1.2441061182752928</v>
+        <v>2.2666590922001908</v>
       </c>
       <c r="I64" s="0">
-        <v>0.95926595300986994</v>
+        <v>2.7665786181009286</v>
       </c>
       <c r="J64" s="0">
-        <v>1.0121457489878534</v>
+        <v>2.4843577475156402</v>
       </c>
       <c r="K64" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L64" s="0">
-        <v>1.1072061704973086</v>
+        <v>2.2455136379186991</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.0928423747169431</v>
+        <v>2.3481342916215398</v>
       </c>
       <c r="B65" s="0">
-        <v>0.087719298245613961</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C65" s="0">
-        <v>0.94218795571843328</v>
+        <v>2.4017550311315112</v>
       </c>
       <c r="D65" s="0">
-        <v>0.81263674175943001</v>
+        <v>2.1349746351549519</v>
       </c>
       <c r="E65" s="0">
-        <v>1.3031415018347792</v>
+        <v>2.5680957069124952</v>
       </c>
       <c r="F65" s="0">
-        <v>1.0260888549285003</v>
+        <v>2.3287122948731924</v>
       </c>
       <c r="G65" s="0">
-        <v>1.0863005431502706</v>
+        <v>2.3938845302755962</v>
       </c>
       <c r="H65" s="0">
-        <v>1.2895529171163995</v>
+        <v>1.96557404987786</v>
       </c>
       <c r="I65" s="0">
-        <v>0.84606065420746279</v>
+        <v>2.4031300272089906</v>
       </c>
       <c r="J65" s="0">
-        <v>0.99374309900625601</v>
+        <v>2.1531100478468881</v>
       </c>
       <c r="K65" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L65" s="0">
-        <v>1.0745498087270229</v>
+        <v>2.1879762386091479</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.021463030422368</v>
+        <v>2.220143743231267</v>
       </c>
       <c r="B66" s="0">
-        <v>0.70175438596491169</v>
+        <v>2.368421052631577</v>
       </c>
       <c r="C66" s="0">
-        <v>0.92570283670855502</v>
+        <v>2.352299674101876</v>
       </c>
       <c r="D66" s="0">
-        <v>0.70925396100305282</v>
+        <v>1.8272305436010852</v>
       </c>
       <c r="E66" s="0">
-        <v>1.1981264357528556</v>
+        <v>2.4374235508219195</v>
       </c>
       <c r="F66" s="0">
-        <v>1.0006185642033247</v>
+        <v>2.1031182913073518</v>
       </c>
       <c r="G66" s="0">
-        <v>1.2673506336753158</v>
+        <v>2.4341178837256066</v>
       </c>
       <c r="H66" s="0">
-        <v>1.1872976197239098</v>
+        <v>1.8405953530648167</v>
       </c>
       <c r="I66" s="0">
-        <v>0.77654862862703744</v>
+        <v>2.5500983098647469</v>
       </c>
       <c r="J66" s="0">
-        <v>1.0857563489142428</v>
+        <v>1.8954729481045254</v>
       </c>
       <c r="K66" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L66" s="0">
-        <v>1.1336422728827782</v>
+        <v>1.9904830031412291</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>0.9451609727281669</v>
+        <v>2.1586098257359439</v>
       </c>
       <c r="B67" s="0">
-        <v>0.26315789473684187</v>
+        <v>2.368421052631577</v>
       </c>
       <c r="C67" s="0">
-        <v>0.83566872519306545</v>
+        <v>2.1544782459833356</v>
       </c>
       <c r="D67" s="0">
-        <v>0.69482845671146531</v>
+        <v>1.6060394777967433</v>
       </c>
       <c r="E67" s="0">
-        <v>1.0978847817655648</v>
+        <v>2.3908827828992489</v>
       </c>
       <c r="F67" s="0">
-        <v>0.94967798275297377</v>
+        <v>2.0339846450533039</v>
       </c>
       <c r="G67" s="0">
-        <v>0.92536712935023058</v>
+        <v>1.890967612150471</v>
       </c>
       <c r="H67" s="0">
-        <v>1.0736806226211433</v>
+        <v>1.7610634550928805</v>
       </c>
       <c r="I67" s="0">
-        <v>0.72888323965760293</v>
+        <v>2.1469285614982798</v>
       </c>
       <c r="J67" s="0">
-        <v>0.84652189915347742</v>
+        <v>1.6562384983437601</v>
       </c>
       <c r="K67" s="0">
         <v>0</v>
       </c>
       <c r="L67" s="0">
-        <v>0.93770410226106349</v>
+        <v>1.9127297608310252</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>0.90085655213153404</v>
+        <v>2.119228118538937</v>
       </c>
       <c r="B68" s="0">
-        <v>0.61403508771929771</v>
+        <v>2.8070175438596467</v>
       </c>
       <c r="C68" s="0">
-        <v>0.78240910993038137</v>
+        <v>2.0961462864099199</v>
       </c>
       <c r="D68" s="0">
-        <v>0.65155194383670267</v>
+        <v>1.6445074892409768</v>
       </c>
       <c r="E68" s="0">
-        <v>1.028670306393388</v>
+        <v>2.3347951907873128</v>
       </c>
       <c r="F68" s="0">
-        <v>0.86235127169522896</v>
+        <v>1.9739475312011046</v>
       </c>
       <c r="G68" s="0">
-        <v>0.68396700865017046</v>
+        <v>1.8507342587004612</v>
       </c>
       <c r="H68" s="0">
-        <v>0.97710617508379172</v>
+        <v>1.8860421519059236</v>
       </c>
       <c r="I68" s="0">
-        <v>0.71299477666779143</v>
+        <v>2.0754304780441286</v>
       </c>
       <c r="J68" s="0">
-        <v>0.95693779904306131</v>
+        <v>1.5274199484725786</v>
       </c>
       <c r="K68" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L68" s="0">
-        <v>0.87394644356669593</v>
+        <v>1.7821043137498818</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>0.74086836664370159</v>
+        <v>2.0453874175445717</v>
       </c>
       <c r="B69" s="0">
-        <v>0.70175438596491946</v>
+        <v>4.6491228070175916</v>
       </c>
       <c r="C69" s="0">
-        <v>0.72788140859002248</v>
+        <v>1.9553887317871337</v>
       </c>
       <c r="D69" s="0">
-        <v>0.62029668453826992</v>
+        <v>1.8801240593369268</v>
       </c>
       <c r="E69" s="0">
-        <v>0.95885915450939263</v>
+        <v>2.1933828574838374</v>
       </c>
       <c r="F69" s="0">
-        <v>0.77320525415712316</v>
+        <v>1.9448386275152112</v>
       </c>
       <c r="G69" s="0">
-        <v>0.82478374572521462</v>
+        <v>1.991550995775518</v>
       </c>
       <c r="H69" s="0">
-        <v>0.85780832812589636</v>
+        <v>1.9144464011816362</v>
       </c>
       <c r="I69" s="0">
-        <v>0.59780341999166464</v>
+        <v>1.9483227741256581</v>
       </c>
       <c r="J69" s="0">
-        <v>1.0489510489510596</v>
+        <v>1.4906146485094007</v>
       </c>
       <c r="K69" s="0">
-        <v>0</v>
+        <v>0.25773195876288924</v>
       </c>
       <c r="L69" s="0">
-        <v>0.77908748794825544</v>
+        <v>1.7525580816720237</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.79009550063995204</v>
+        <v>1.9100127990548375</v>
       </c>
       <c r="B70" s="0">
-        <v>0.96491228070175361</v>
+        <v>2.6315789473684186</v>
       </c>
       <c r="C70" s="0">
-        <v>0.71520054781318487</v>
+        <v>1.9224184937673552</v>
       </c>
       <c r="D70" s="0">
-        <v>0.55538191522611935</v>
+        <v>1.8079965378789684</v>
       </c>
       <c r="E70" s="0">
-        <v>0.85384408842745829</v>
+        <v>2.1808526507354018</v>
       </c>
       <c r="F70" s="0">
-        <v>0.7823017865589631</v>
+        <v>1.7901975766837666</v>
       </c>
       <c r="G70" s="0">
-        <v>0.64373365520016035</v>
+        <v>1.890967612150471</v>
       </c>
       <c r="H70" s="0">
-        <v>0.90325512696699339</v>
+        <v>2.0791910469806267</v>
       </c>
       <c r="I70" s="0">
-        <v>0.63951063533991326</v>
+        <v>1.7814939127326153</v>
       </c>
       <c r="J70" s="0">
-        <v>0.75450864924549066</v>
+        <v>1.7482517482517468</v>
       </c>
       <c r="K70" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L70" s="0">
-        <v>0.83973501695020603</v>
+        <v>1.6110471806674325</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.718716156345377</v>
+        <v>1.7943290341636293</v>
       </c>
       <c r="B71" s="0">
-        <v>1.4912280701754372</v>
+        <v>2.7192982456140329</v>
       </c>
       <c r="C71" s="0">
-        <v>0.63657921099684189</v>
+        <v>1.664997019997716</v>
       </c>
       <c r="D71" s="0">
-        <v>0.41833962445603795</v>
+        <v>1.6445074892409768</v>
       </c>
       <c r="E71" s="0">
-        <v>0.78522628956711049</v>
+        <v>2.0668874369760415</v>
       </c>
       <c r="F71" s="0">
-        <v>0.7568314958337875</v>
+        <v>1.6919550267438037</v>
       </c>
       <c r="G71" s="0">
-        <v>0.70408368537517541</v>
+        <v>2.2731844699255661</v>
       </c>
       <c r="H71" s="0">
-        <v>0.78963812986422699</v>
+        <v>2.0451059478497968</v>
       </c>
       <c r="I71" s="0">
-        <v>0.59780341999165798</v>
+        <v>1.6106929355921416</v>
       </c>
       <c r="J71" s="0">
-        <v>0.68089804931910136</v>
+        <v>1.9690835480309146</v>
       </c>
       <c r="K71" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L71" s="0">
-        <v>0.75731658010138958</v>
+        <v>1.494417317202126</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.66210495224967947</v>
+        <v>1.7869449640641906</v>
       </c>
       <c r="B72" s="0">
-        <v>1.2280701754385954</v>
+        <v>2.8070175438596467</v>
       </c>
       <c r="C72" s="0">
-        <v>0.58458768181184084</v>
+        <v>1.7360098403479614</v>
       </c>
       <c r="D72" s="0">
-        <v>0.42795662731709622</v>
+        <v>1.4473589305892804</v>
       </c>
       <c r="E72" s="0">
-        <v>0.70407828395835137</v>
+        <v>2.0119931978877634</v>
       </c>
       <c r="F72" s="0">
-        <v>0.6531310264527157</v>
+        <v>1.7247025433904579</v>
       </c>
       <c r="G72" s="0">
-        <v>0.70408368537517541</v>
+        <v>1.911084288875476</v>
       </c>
       <c r="H72" s="0">
-        <v>0.78963812986422699</v>
+        <v>1.9201272510367535</v>
       </c>
       <c r="I72" s="0">
-        <v>0.5223332207900534</v>
+        <v>1.65637226668785</v>
       </c>
       <c r="J72" s="0">
-        <v>0.42326094957673871</v>
+        <v>1.6746411483253574</v>
       </c>
       <c r="K72" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L72" s="0">
-        <v>0.70599944017665472</v>
+        <v>1.5519547165116772</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.6128778182534208</v>
+        <v>1.6712611991729829</v>
       </c>
       <c r="B73" s="0">
-        <v>1.3157894736842093</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C73" s="0">
-        <v>0.502162086762449</v>
+        <v>1.6041288882689342</v>
       </c>
       <c r="D73" s="0">
-        <v>0.33659510013704197</v>
+        <v>1.2934868848123471</v>
       </c>
       <c r="E73" s="0">
-        <v>0.68558131209164896</v>
+        <v>1.881321041797188</v>
       </c>
       <c r="F73" s="0">
-        <v>0.63311865516864907</v>
+        <v>1.622821380489756</v>
       </c>
       <c r="G73" s="0">
-        <v>0.70408368537517541</v>
+        <v>1.8105009052504511</v>
       </c>
       <c r="H73" s="0">
-        <v>0.74419133102312041</v>
+        <v>1.7440209055274654</v>
       </c>
       <c r="I73" s="0">
-        <v>0.45282119520962805</v>
+        <v>1.3604496435026103</v>
       </c>
       <c r="J73" s="0">
-        <v>0.68089804931910136</v>
+        <v>1.7298490982701495</v>
       </c>
       <c r="K73" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L73" s="0">
-        <v>0.67489814325257302</v>
+        <v>1.3700121295057992</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.54642118735847156</v>
+        <v>1.540809294082897</v>
       </c>
       <c r="B74" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C74" s="0">
-        <v>0.502162086762449</v>
+        <v>1.5191671210641766</v>
       </c>
       <c r="D74" s="0">
-        <v>0.28370158440122112</v>
+        <v>1.0698915682927406</v>
       </c>
       <c r="E74" s="0">
-        <v>0.56087592111936468</v>
+        <v>1.7918195650228215</v>
       </c>
       <c r="F74" s="0">
-        <v>0.61674489684532197</v>
+        <v>1.566422879598296</v>
       </c>
       <c r="G74" s="0">
-        <v>0.78455039227519552</v>
+        <v>1.6294508147254059</v>
       </c>
       <c r="H74" s="0">
-        <v>0.70442538203715221</v>
+        <v>1.4656592626256875</v>
       </c>
       <c r="I74" s="0">
-        <v>0.43494667434609008</v>
+        <v>1.499473694663461</v>
       </c>
       <c r="J74" s="0">
-        <v>0.44166359955833606</v>
+        <v>1.9506808980493173</v>
       </c>
       <c r="K74" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L74" s="0">
-        <v>0.59558983609616467</v>
+        <v>1.2782633035797581</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.53903711725903269</v>
+        <v>1.4202028157920632</v>
       </c>
       <c r="B75" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C75" s="0">
-        <v>0.38423008153793448</v>
+        <v>1.4215244930825892</v>
       </c>
       <c r="D75" s="0">
-        <v>0.23321231938066481</v>
+        <v>0.79099848532204875</v>
       </c>
       <c r="E75" s="0">
-        <v>0.48808138667621304</v>
+        <v>1.6915779110355307</v>
       </c>
       <c r="F75" s="0">
-        <v>0.59309391260051614</v>
+        <v>1.4463486518938966</v>
       </c>
       <c r="G75" s="0">
-        <v>0.64373365520016035</v>
+        <v>1.4081673707503508</v>
       </c>
       <c r="H75" s="0">
-        <v>0.64761688348576885</v>
+        <v>1.3293188661023678</v>
       </c>
       <c r="I75" s="0">
-        <v>0.39125340112410839</v>
+        <v>1.2472443447002035</v>
       </c>
       <c r="J75" s="0">
-        <v>0.47846889952153066</v>
+        <v>1.2329775487670214</v>
       </c>
       <c r="K75" s="0">
-        <v>0</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L75" s="0">
-        <v>0.64224178148228728</v>
+        <v>1.2751531738873501</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.52180762036034212</v>
+        <v>1.3685143250959917</v>
       </c>
       <c r="B76" s="0">
-        <v>0.61403508771929771</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C76" s="0">
-        <v>0.32589812196451867</v>
+        <v>1.4291330095486869</v>
       </c>
       <c r="D76" s="0">
-        <v>0.26206332796383985</v>
+        <v>0.88476426321736745</v>
       </c>
       <c r="E76" s="0">
-        <v>0.45228079596646636</v>
+        <v>1.6414570840418852</v>
       </c>
       <c r="F76" s="0">
-        <v>0.47301968489611723</v>
+        <v>1.4681803296583331</v>
       </c>
       <c r="G76" s="0">
-        <v>0.5833836250251454</v>
+        <v>1.2874673104003207</v>
       </c>
       <c r="H76" s="0">
-        <v>0.61353178435493894</v>
+        <v>1.3747656649434743</v>
       </c>
       <c r="I76" s="0">
-        <v>0.37337888026057048</v>
+        <v>1.2273837659629392</v>
       </c>
       <c r="J76" s="0">
-        <v>0.69930069930069871</v>
+        <v>1.10415899889584</v>
       </c>
       <c r="K76" s="0">
-        <v>0</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L76" s="0">
-        <v>0.51628152893975632</v>
+        <v>1.2160607097315947</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.4331987791670765</v>
+        <v>1.3020576942010424</v>
       </c>
       <c r="B77" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C77" s="0">
-        <v>0.27771085101256648</v>
+        <v>1.2097541181095362</v>
       </c>
       <c r="D77" s="0">
-        <v>0.28851008583175031</v>
+        <v>0.81023249104416539</v>
       </c>
       <c r="E77" s="0">
-        <v>0.42304364688683993</v>
+        <v>1.5095915749276516</v>
       </c>
       <c r="F77" s="0">
-        <v>0.45846523305315967</v>
+        <v>1.2207546483280563</v>
       </c>
       <c r="G77" s="0">
-        <v>0.30175015087507517</v>
+        <v>1.2874673104003207</v>
       </c>
       <c r="H77" s="0">
-        <v>0.53968073623814072</v>
+        <v>1.2100210191444629</v>
       </c>
       <c r="I77" s="0">
-        <v>0.34954618577585322</v>
+        <v>1.0565827888224653</v>
       </c>
       <c r="J77" s="0">
-        <v>0.49687154950312801</v>
+        <v>1.324990798675008</v>
       </c>
       <c r="K77" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L77" s="0">
-        <v>0.47118464839983787</v>
+        <v>1.1787391534226968</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.43812149256670241</v>
+        <v>1.1543762922122665</v>
       </c>
       <c r="B78" s="0">
         <v>0.17543859649122792</v>
       </c>
       <c r="C78" s="0">
-        <v>0.25361721553659039</v>
+        <v>1.2059498598764875</v>
       </c>
       <c r="D78" s="0">
-        <v>0.2163825643738127</v>
+        <v>0.75493472459307986</v>
       </c>
       <c r="E78" s="0">
-        <v>0.34189564127808075</v>
+        <v>1.4206867746651142</v>
       </c>
       <c r="F78" s="0">
-        <v>0.38933158679911184</v>
+        <v>1.2425863260924923</v>
       </c>
       <c r="G78" s="0">
-        <v>0.34198350432508523</v>
+        <v>1.3679340173003409</v>
       </c>
       <c r="H78" s="0">
-        <v>0.54536158609327912</v>
+        <v>1.1816167698687712</v>
       </c>
       <c r="I78" s="0">
-        <v>0.27804810232170141</v>
+        <v>1.0883597148020883</v>
       </c>
       <c r="J78" s="0">
-        <v>0.5152741994847253</v>
+        <v>0.99374309900625601</v>
       </c>
       <c r="K78" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L78" s="0">
-        <v>0.44785867570677662</v>
+        <v>1.1025409759586966</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.33966722457418502</v>
+        <v>1.1002264448163819</v>
       </c>
       <c r="B79" s="0">
-        <v>0</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C79" s="0">
-        <v>0.20162568635158939</v>
+        <v>1.0930901989627047</v>
       </c>
       <c r="D79" s="0">
-        <v>0.26206332796383985</v>
+        <v>0.77897723174572575</v>
       </c>
       <c r="E79" s="0">
-        <v>0.31504519824577076</v>
+        <v>1.3359587099853803</v>
       </c>
       <c r="F79" s="0">
-        <v>0.35658407015245758</v>
+        <v>1.1552596150347478</v>
       </c>
       <c r="G79" s="0">
-        <v>0.34198350432508523</v>
+        <v>1.0058338362502506</v>
       </c>
       <c r="H79" s="0">
-        <v>0.50559563710731081</v>
+        <v>1.1248082713173882</v>
       </c>
       <c r="I79" s="0">
-        <v>0.28400627594288075</v>
+        <v>0.97714047387340786</v>
       </c>
       <c r="J79" s="0">
-        <v>0.62569009937430942</v>
+        <v>0.93853514906146396</v>
       </c>
       <c r="K79" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L79" s="0">
-        <v>0.36855036855036821</v>
+        <v>1.1118713650359211</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.34705129467362378</v>
+        <v>1.0436152407206842</v>
       </c>
       <c r="B80" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C80" s="0">
-        <v>0.13948946854512473</v>
+        <v>1.0208092925347763</v>
       </c>
       <c r="D80" s="0">
-        <v>0.2163825643738127</v>
+        <v>0.64674344240617354</v>
       </c>
       <c r="E80" s="0">
-        <v>0.29416152033175191</v>
+        <v>1.2935946776455134</v>
       </c>
       <c r="F80" s="0">
-        <v>0.38933158679911184</v>
+        <v>1.1225120983880936</v>
       </c>
       <c r="G80" s="0">
-        <v>0.26151679742506517</v>
+        <v>1.3075839871253259</v>
       </c>
       <c r="H80" s="0">
-        <v>0.4317445889905126</v>
+        <v>1.2952337669715377</v>
       </c>
       <c r="I80" s="0">
-        <v>0.21648030823618181</v>
+        <v>0.9374193163988791</v>
       </c>
       <c r="J80" s="0">
-        <v>0.42326094957673871</v>
+        <v>1.1409642988590347</v>
       </c>
       <c r="K80" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L80" s="0">
-        <v>0.37321556308898052</v>
+        <v>1.0310079930333087</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.28305602047848749</v>
+        <v>0.866397558334153</v>
       </c>
       <c r="B81" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C81" s="0">
-        <v>0.12554052169061225</v>
+        <v>1.0182731203794104</v>
       </c>
       <c r="D81" s="0">
-        <v>0.18512730507537309</v>
+        <v>0.5890414252398235</v>
       </c>
       <c r="E81" s="0">
-        <v>0.23091381007786607</v>
+        <v>1.1784361108624948</v>
       </c>
       <c r="F81" s="0">
-        <v>0.27107666557508253</v>
+        <v>1.057017065094785</v>
       </c>
       <c r="G81" s="0">
-        <v>0.36210018105009018</v>
+        <v>1.1265338966002805</v>
       </c>
       <c r="H81" s="0">
-        <v>0.32380844174288442</v>
+        <v>1.0623189229108665</v>
       </c>
       <c r="I81" s="0">
-        <v>0.21648030823618181</v>
+        <v>0.83613036483883063</v>
       </c>
       <c r="J81" s="0">
-        <v>0.20242914979757068</v>
+        <v>1.0305483989694506</v>
       </c>
       <c r="K81" s="0">
         <v>0</v>
       </c>
       <c r="L81" s="0">
-        <v>0.29235219108636806</v>
+        <v>0.94703449133828799</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.23382888648223141</v>
+        <v>0.92054740573004767</v>
       </c>
       <c r="B82" s="0">
-        <v>0.087719298245614932</v>
+        <v>0.26315789473684481</v>
       </c>
       <c r="C82" s="0">
-        <v>0.095106455826222458</v>
+        <v>0.98403479628198165</v>
       </c>
       <c r="D82" s="0">
-        <v>0.117808285047966</v>
+        <v>0.50970115163609786</v>
       </c>
       <c r="E82" s="0">
-        <v>0.21420686774665337</v>
+        <v>1.0513440138429058</v>
       </c>
       <c r="F82" s="0">
-        <v>0.27471527853582495</v>
+        <v>1.03700469381073</v>
       </c>
       <c r="G82" s="0">
-        <v>0.16093341380004189</v>
+        <v>1.207000603500314</v>
       </c>
       <c r="H82" s="0">
-        <v>0.23859569391581223</v>
+        <v>1.2157018689996149</v>
       </c>
       <c r="I82" s="0">
-        <v>0.22442453973109006</v>
+        <v>0.80038132311176358</v>
       </c>
       <c r="J82" s="0">
-        <v>0.16562384983437783</v>
+        <v>0.90172984909827925</v>
       </c>
       <c r="K82" s="0">
-        <v>0.12886597938144462</v>
+        <v>0</v>
       </c>
       <c r="L82" s="0">
-        <v>0.32656361770286152</v>
+        <v>0.88794202718254267</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.25844245348035816</v>
+        <v>0.79747957073939091</v>
       </c>
       <c r="B83" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C83" s="0">
-        <v>0.084961767204757788</v>
+        <v>0.85976236066904144</v>
       </c>
       <c r="D83" s="0">
-        <v>0.091361527180054247</v>
+        <v>0.49287139662924007</v>
       </c>
       <c r="E83" s="0">
-        <v>0.16527939377666384</v>
+        <v>1.0233002177869259</v>
       </c>
       <c r="F83" s="0">
-        <v>0.23105192300694952</v>
+        <v>0.93148491794927679</v>
       </c>
       <c r="G83" s="0">
-        <v>0.28163347415007012</v>
+        <v>1.3880506940253456</v>
       </c>
       <c r="H83" s="0">
-        <v>0.32948929159802276</v>
+        <v>0.94302107595296181</v>
       </c>
       <c r="I83" s="0">
-        <v>0.15491251415066221</v>
+        <v>0.74079958689996162</v>
       </c>
       <c r="J83" s="0">
-        <v>0.165623849834376</v>
+        <v>1.0121457489878534</v>
       </c>
       <c r="K83" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L83" s="0">
-        <v>0.26902621839330676</v>
+        <v>0.74021086679314463</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.16983361228709251</v>
+        <v>0.70640937284631222</v>
       </c>
       <c r="B84" s="0">
-        <v>0</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C84" s="0">
-        <v>0.073548992505611213</v>
+        <v>0.82806020872696773</v>
       </c>
       <c r="D84" s="0">
-        <v>0.079340273603731332</v>
+        <v>0.35823335657442323</v>
       </c>
       <c r="E84" s="0">
-        <v>0.15274918702825249</v>
+        <v>0.91709179868134416</v>
       </c>
       <c r="F84" s="0">
-        <v>0.17465342211548943</v>
+        <v>0.85689335225412</v>
       </c>
       <c r="G84" s="0">
-        <v>0.24140012070006014</v>
+        <v>0.72420036210018035</v>
       </c>
       <c r="H84" s="0">
-        <v>0.2556382434812246</v>
+        <v>0.97710617508379172</v>
       </c>
       <c r="I84" s="0">
-        <v>0.1390240511608507</v>
+        <v>0.74079958689996162</v>
       </c>
       <c r="J84" s="0">
-        <v>0.165623849834376</v>
+        <v>1.10415899889584</v>
       </c>
       <c r="K84" s="0">
         <v>0</v>
       </c>
       <c r="L84" s="0">
-        <v>0.19749323546791883</v>
+        <v>0.81174384971853253</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.16983361228709251</v>
+        <v>0.63010731515211127</v>
       </c>
       <c r="B85" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C85" s="0">
-        <v>0.041846840563537414</v>
+        <v>0.8077708314840405</v>
       </c>
       <c r="D85" s="0">
-        <v>0.084148775034260492</v>
+        <v>0.32216959584545446</v>
       </c>
       <c r="E85" s="0">
-        <v>0.12768877353142982</v>
+        <v>0.80073987887466747</v>
       </c>
       <c r="F85" s="0">
-        <v>0.12553214714550803</v>
+        <v>0.8732671105774471</v>
       </c>
       <c r="G85" s="0">
-        <v>0.28163347415007012</v>
+        <v>0.72420036210018035</v>
       </c>
       <c r="H85" s="0">
-        <v>0.26699994319150122</v>
+        <v>0.75555303073339708</v>
       </c>
       <c r="I85" s="0">
-        <v>0.10128895156004836</v>
+        <v>0.6454688089610926</v>
       </c>
       <c r="J85" s="0">
-        <v>0.20242914979757068</v>
+        <v>0.68089804931910136</v>
       </c>
       <c r="K85" s="0">
         <v>0</v>
       </c>
       <c r="L85" s="0">
-        <v>0.19127297608310248</v>
+        <v>0.73710073710073643</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.15998818548784075</v>
+        <v>0.65718223885005356</v>
       </c>
       <c r="B86" s="0">
-        <v>0.17543859649122792</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C86" s="0">
-        <v>0.022825549398293135</v>
+        <v>0.75958356053208831</v>
       </c>
       <c r="D86" s="0">
-        <v>0.079340273603731332</v>
+        <v>0.32216959584545446</v>
       </c>
       <c r="E86" s="0">
-        <v>0.11098183120021471</v>
+        <v>0.7362988155971234</v>
       </c>
       <c r="F86" s="0">
-        <v>0.10733908234181121</v>
+        <v>0.75501218935341785</v>
       </c>
       <c r="G86" s="0">
-        <v>0.10058338362502504</v>
+        <v>0.70408368537517541</v>
       </c>
       <c r="H86" s="0">
-        <v>0.18178719536442633</v>
+        <v>0.65897858319604552</v>
       </c>
       <c r="I86" s="0">
-        <v>0.10724712518122768</v>
+        <v>0.62560823022382817</v>
       </c>
       <c r="J86" s="0">
-        <v>0.14722119985277868</v>
+        <v>0.84652189915347742</v>
       </c>
       <c r="K86" s="0">
         <v>0</v>
       </c>
       <c r="L86" s="0">
-        <v>0.16328180885142896</v>
+        <v>0.66090255963673628</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.091070197893078589</v>
+        <v>0.60795510485379489</v>
       </c>
       <c r="B87" s="0">
-        <v>0.087719298245613961</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C87" s="0">
-        <v>0.021557463320610183</v>
+        <v>0.63657921099684189</v>
       </c>
       <c r="D87" s="0">
-        <v>0.096170028610583422</v>
+        <v>0.23802082081119397</v>
       </c>
       <c r="E87" s="0">
-        <v>0.074584563978638913</v>
+        <v>0.68558131209164897</v>
       </c>
       <c r="F87" s="0">
-        <v>0.063675726812938857</v>
+        <v>0.70589091438343643</v>
       </c>
       <c r="G87" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.80466706900020035</v>
       </c>
       <c r="H87" s="0">
-        <v>0.10225529739248983</v>
+        <v>0.72714878145770534</v>
       </c>
       <c r="I87" s="0">
-        <v>0.081428372822783979</v>
+        <v>0.54417985740104413</v>
       </c>
       <c r="J87" s="0">
-        <v>0.12881854987118133</v>
+        <v>0.66249539933750401</v>
       </c>
       <c r="K87" s="0">
         <v>0</v>
       </c>
       <c r="L87" s="0">
-        <v>0.11040960408049005</v>
+        <v>0.65157217055951178</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.08122477109382685</v>
+        <v>0.6178005316530466</v>
       </c>
       <c r="B88" s="0">
-        <v>0.087719298245613961</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C88" s="0">
-        <v>0.020289377242927231</v>
+        <v>0.5693706488796455</v>
       </c>
       <c r="D88" s="0">
-        <v>0.074531772173202157</v>
+        <v>0.31495684369966071</v>
       </c>
       <c r="E88" s="0">
-        <v>0.066827769324860467</v>
+        <v>0.57280945135594685</v>
       </c>
       <c r="F88" s="0">
-        <v>0.052759887930720763</v>
+        <v>0.64039588109012779</v>
       </c>
       <c r="G88" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.68396700865017046</v>
       </c>
       <c r="H88" s="0">
-        <v>0.16474464579901138</v>
+        <v>0.75555303073339708</v>
       </c>
       <c r="I88" s="0">
-        <v>0.051637504716887404</v>
+        <v>0.52829139441123263</v>
       </c>
       <c r="J88" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.62569009937430942</v>
       </c>
       <c r="K88" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L88" s="0">
-        <v>0.08552856654122469</v>
+        <v>0.60025503063477692</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.044304420596632824</v>
+        <v>0.48734862656296107</v>
       </c>
       <c r="B89" s="0">
-        <v>0.26315789473684187</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C89" s="0">
-        <v>0.0063404303884147598</v>
+        <v>0.60741323121013402</v>
       </c>
       <c r="D89" s="0">
-        <v>0.06010626788161464</v>
+        <v>0.29572283797754406</v>
       </c>
       <c r="E89" s="0">
-        <v>0.048330797458158013</v>
+        <v>0.56445598019033927</v>
       </c>
       <c r="F89" s="0">
-        <v>0.027289597205545222</v>
+        <v>0.63129934868827942</v>
       </c>
       <c r="G89" s="0">
-        <v>0.14081673707503506</v>
+        <v>0.62361697847515529</v>
       </c>
       <c r="H89" s="0">
-        <v>0.090893597682213167</v>
+        <v>0.63625518377549228</v>
       </c>
       <c r="I89" s="0">
-        <v>0.053623562590613842</v>
+        <v>0.48459812118925105</v>
       </c>
       <c r="J89" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.62569009937430942</v>
       </c>
       <c r="K89" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L89" s="0">
-        <v>0.065312723540571577</v>
+        <v>0.55982334463347072</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.029536280397755216</v>
+        <v>0.44058284926651536</v>
       </c>
       <c r="B90" s="0">
-        <v>0</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C90" s="0">
-        <v>0.0050723443107318078</v>
+        <v>0.46665567658732632</v>
       </c>
       <c r="D90" s="0">
-        <v>0.067319020027408402</v>
+        <v>0.2548505758180461</v>
       </c>
       <c r="E90" s="0">
-        <v>0.034607237686088456</v>
+        <v>0.46660103225036509</v>
       </c>
       <c r="F90" s="0">
-        <v>0.040024742568132987</v>
+        <v>0.60582905796310393</v>
       </c>
       <c r="G90" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.98571715952524564</v>
       </c>
       <c r="H90" s="0">
-        <v>0.096574447537351504</v>
+        <v>0.72714878145770534</v>
       </c>
       <c r="I90" s="0">
-        <v>0.037735099600802333</v>
+        <v>0.4150860956088257</v>
       </c>
       <c r="J90" s="0">
-        <v>0.055207949944792008</v>
+        <v>0.49687154950312801</v>
       </c>
       <c r="K90" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L90" s="0">
-        <v>0.04043168600130622</v>
+        <v>0.57070879855689938</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.03692035049719402</v>
+        <v>0.44796691936595412</v>
       </c>
       <c r="B91" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C91" s="0">
-        <v>0</v>
+        <v>0.43495352464525255</v>
       </c>
       <c r="D91" s="0">
-        <v>0.028851008583175027</v>
+        <v>0.23802082081119397</v>
       </c>
       <c r="E91" s="0">
-        <v>0.022673707449506232</v>
+        <v>0.42006026432769439</v>
       </c>
       <c r="F91" s="0">
-        <v>0.020012371284066494</v>
+        <v>0.52577957282683796</v>
       </c>
       <c r="G91" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.64373365520016035</v>
       </c>
       <c r="H91" s="0">
-        <v>0.05680849855138323</v>
+        <v>0.5510424359484174</v>
       </c>
       <c r="I91" s="0">
-        <v>0.019860578737264385</v>
+        <v>0.37735099600802335</v>
       </c>
       <c r="J91" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.38645564961354401</v>
       </c>
       <c r="K91" s="0">
-        <v>1.1597938144329887</v>
+        <v>0</v>
       </c>
       <c r="L91" s="0">
-        <v>0.023325972693061282</v>
+        <v>0.46340932416881747</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.034458993797381085</v>
+        <v>0.38889435857044369</v>
       </c>
       <c r="B92" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C92" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0.39564285623708101</v>
       </c>
       <c r="D92" s="0">
-        <v>0.016829755006852101</v>
+        <v>0.22359531651960646</v>
       </c>
       <c r="E92" s="0">
-        <v>0.016110265819386006</v>
+        <v>0.38008293803514393</v>
       </c>
       <c r="F92" s="0">
-        <v>0.01455445184295745</v>
+        <v>0.54033402466979541</v>
       </c>
       <c r="G92" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H92" s="0">
-        <v>0.034085099130829945</v>
+        <v>0.50559563710731081</v>
       </c>
       <c r="I92" s="0">
-        <v>0.0099302893686321926</v>
+        <v>0.34954618577585323</v>
       </c>
       <c r="J92" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.55207949944792001</v>
       </c>
       <c r="K92" s="0">
-        <v>1.417525773195875</v>
+        <v>0</v>
       </c>
       <c r="L92" s="0">
-        <v>0.02021584300065311</v>
+        <v>0.43386309209093982</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.012306783499064673</v>
+        <v>0.36674214827212726</v>
       </c>
       <c r="B93" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C93" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0.34238324097439704</v>
       </c>
       <c r="D93" s="0">
-        <v>0.024042507152645855</v>
+        <v>0.1538720457769335</v>
       </c>
       <c r="E93" s="0">
-        <v>0.0053700886064620016</v>
+        <v>0.33473552313613147</v>
       </c>
       <c r="F93" s="0">
-        <v>0.0036386129607393625</v>
+        <v>0.50576720154277144</v>
       </c>
       <c r="G93" s="0">
-        <v>0</v>
+        <v>0.38221685777509523</v>
       </c>
       <c r="H93" s="0">
-        <v>0.039765948985968268</v>
+        <v>0.48287223768675752</v>
       </c>
       <c r="I93" s="0">
-        <v>0.0079442314949057548</v>
+        <v>0.32968560703858879</v>
       </c>
       <c r="J93" s="0">
-        <v>0.018402649981597335</v>
+        <v>0.49687154950312801</v>
       </c>
       <c r="K93" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L93" s="0">
-        <v>0.010885453923428597</v>
+        <v>0.43075296239853161</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.014768140198877771</v>
+        <v>0.31259230087624618</v>
       </c>
       <c r="B94" s="0">
         <v>0.087719298245614932</v>
       </c>
       <c r="C94" s="0">
-        <v>0</v>
+        <v>0.25615338769195911</v>
       </c>
       <c r="D94" s="0">
-        <v>0.0096170028610584497</v>
+        <v>0.14665929363114136</v>
       </c>
       <c r="E94" s="0">
-        <v>0.0071601181419494158</v>
+        <v>0.30132163847370458</v>
       </c>
       <c r="F94" s="0">
-        <v>0.0054579194411091053</v>
+        <v>0.42389840992614047</v>
       </c>
       <c r="G94" s="0">
-        <v>0</v>
+        <v>0.38221685777509945</v>
       </c>
       <c r="H94" s="0">
-        <v>0.028404249275691931</v>
+        <v>0.45446798841107089</v>
       </c>
       <c r="I94" s="0">
-        <v>0.013902405116085224</v>
+        <v>0.31776925979623372</v>
       </c>
       <c r="J94" s="0">
-        <v>0</v>
+        <v>0.46006624953993841</v>
       </c>
       <c r="K94" s="0">
-        <v>2.0618556701031139</v>
+        <v>0</v>
       </c>
       <c r="L94" s="0">
-        <v>0.0093303890772246153</v>
+        <v>0.32967374739526972</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.27813330707886164</v>
       </c>
       <c r="B95" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C95" s="0">
-        <v>0</v>
+        <v>0.24220444083744383</v>
       </c>
       <c r="D95" s="0">
-        <v>0</v>
+        <v>0.10578703147164176</v>
       </c>
       <c r="E95" s="0">
-        <v>0.0023867060473164452</v>
+        <v>0.23389719263701167</v>
       </c>
       <c r="F95" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.37841574791689375</v>
       </c>
       <c r="G95" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.28163347415007012</v>
       </c>
       <c r="H95" s="0">
-        <v>0.011361699710276646</v>
+        <v>0.36357439072885267</v>
       </c>
       <c r="I95" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.28996444956406003</v>
       </c>
       <c r="J95" s="0">
-        <v>0</v>
+        <v>0.29444239970555736</v>
       </c>
       <c r="K95" s="0">
-        <v>1.0309278350515454</v>
+        <v>0</v>
       </c>
       <c r="L95" s="0">
-        <v>0.0031101296924081708</v>
+        <v>0.37477062793518456</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.0049227133996258693</v>
+        <v>0.27074923697942282</v>
       </c>
       <c r="B96" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C96" s="0">
-        <v>0</v>
+        <v>0.15217032932195424</v>
       </c>
       <c r="D96" s="0">
-        <v>0.004808501430529172</v>
+        <v>0.086553025749525073</v>
       </c>
       <c r="E96" s="0">
-        <v>0.0023867060473164452</v>
+        <v>0.20764342611653075</v>
       </c>
       <c r="F96" s="0">
-        <v>0</v>
+        <v>0.35112615071134851</v>
       </c>
       <c r="G96" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.30175015087507517</v>
       </c>
       <c r="H96" s="0">
-        <v>0.005680849855138323</v>
+        <v>0.30676589217746947</v>
       </c>
       <c r="I96" s="0">
-        <v>0.0079442314949057548</v>
+        <v>0.25222934996325769</v>
       </c>
       <c r="J96" s="0">
-        <v>0</v>
+        <v>0.4600662495399333</v>
       </c>
       <c r="K96" s="0">
-        <v>0.90206185567010222</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L96" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0.27213634808571496</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.19936989268484773</v>
       </c>
       <c r="B97" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C97" s="0">
-        <v>0</v>
+        <v>0.15977884578805196</v>
       </c>
       <c r="D97" s="0">
-        <v>0</v>
+        <v>0.098574279325848016</v>
       </c>
       <c r="E97" s="0">
-        <v>0.001790029535487334</v>
+        <v>0.21420686774665099</v>
       </c>
       <c r="F97" s="0">
-        <v>0</v>
+        <v>0.23105192300694952</v>
       </c>
       <c r="G97" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.26151679742506517</v>
       </c>
       <c r="H97" s="0">
-        <v>0</v>
+        <v>0.30108504232233119</v>
       </c>
       <c r="I97" s="0">
-        <v>0</v>
+        <v>0.19661972949891743</v>
       </c>
       <c r="J97" s="0">
-        <v>0</v>
+        <v>0.20242914979757068</v>
       </c>
       <c r="K97" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L97" s="0">
-        <v>0</v>
+        <v>0.22392933785338831</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0</v>
+        <v>0.19444717928522184</v>
       </c>
       <c r="B98" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C98" s="0">
-        <v>0</v>
+        <v>0.12807669384597814</v>
       </c>
       <c r="D98" s="0">
-        <v>0</v>
+        <v>0.050489265020556291</v>
       </c>
       <c r="E98" s="0">
-        <v>0</v>
+        <v>0.1736328649422714</v>
       </c>
       <c r="F98" s="0">
-        <v>0</v>
+        <v>0.31837863406469424</v>
       </c>
       <c r="G98" s="0">
-        <v>0</v>
+        <v>0.28163347415007012</v>
       </c>
       <c r="H98" s="0">
-        <v>0.011361699710276646</v>
+        <v>0.20451059478497965</v>
       </c>
       <c r="I98" s="0">
-        <v>0</v>
+        <v>0.22641059760481402</v>
       </c>
       <c r="J98" s="0">
-        <v>0</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K98" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L98" s="0">
-        <v>0</v>
+        <v>0.21148881908375561</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0</v>
+        <v>0.14029733188933727</v>
       </c>
       <c r="B99" s="0">
         <v>0</v>
       </c>
       <c r="C99" s="0">
-        <v>0</v>
+        <v>0.073548992505611213</v>
       </c>
       <c r="D99" s="0">
-        <v>0.002404250715264586</v>
+        <v>0.088957276464789667</v>
       </c>
       <c r="E99" s="0">
-        <v>0</v>
+        <v>0.15811927563471448</v>
       </c>
       <c r="F99" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.2383291489284283</v>
       </c>
       <c r="G99" s="0">
-        <v>0</v>
+        <v>0.42245021122510523</v>
       </c>
       <c r="H99" s="0">
-        <v>0</v>
+        <v>0.22155314435039461</v>
       </c>
       <c r="I99" s="0">
-        <v>0</v>
+        <v>0.14696828265575645</v>
       </c>
       <c r="J99" s="0">
-        <v>0</v>
+        <v>0.20242914979757068</v>
       </c>
       <c r="K99" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L99" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0.16950206823624531</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0</v>
+        <v>0.48980998326277397</v>
       </c>
       <c r="B100" s="0">
-        <v>0</v>
+        <v>1.9298245614035072</v>
       </c>
       <c r="C100" s="0">
-        <v>0</v>
+        <v>0.2662980763134199</v>
       </c>
       <c r="D100" s="0">
-        <v>0</v>
+        <v>0.3341908494217774</v>
       </c>
       <c r="E100" s="0">
-        <v>0.0005966765118291113</v>
+        <v>0.43855723619439679</v>
       </c>
       <c r="F100" s="0">
-        <v>0</v>
+        <v>0.71862605974602412</v>
       </c>
       <c r="G100" s="0">
-        <v>0</v>
+        <v>1.2673506336753158</v>
       </c>
       <c r="H100" s="0">
-        <v>0</v>
+        <v>0.95438277566323837</v>
       </c>
       <c r="I100" s="0">
-        <v>0</v>
+        <v>0.61170582510774307</v>
       </c>
       <c r="J100" s="0">
-        <v>0</v>
+        <v>1.0305483989694506</v>
       </c>
       <c r="K100" s="0">
-        <v>0.12886597938144317</v>
+        <v>9.7938144329896826</v>
       </c>
       <c r="L100" s="0">
-        <v>0</v>
+        <v>0.49917581563151142</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0003_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0003_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
